--- a/output/yearly_total_coral_cover_iteration_18_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_18_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.284171584821121</v>
+        <v>1.252078252369293</v>
       </c>
       <c r="C3" t="n">
-        <v>4.653481063946931</v>
+        <v>4.681068174436266</v>
       </c>
       <c r="D3" t="n">
-        <v>6.088922074136388</v>
+        <v>6.09171023761645</v>
       </c>
       <c r="E3" t="n">
-        <v>12.02657472290444</v>
+        <v>12.02485666442201</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.451919438406175</v>
+        <v>1.370120514045453</v>
       </c>
       <c r="C4" t="n">
-        <v>5.195667952924744</v>
+        <v>5.300078362317505</v>
       </c>
       <c r="D4" t="n">
-        <v>6.456212911080534</v>
+        <v>6.294764535747397</v>
       </c>
       <c r="E4" t="n">
-        <v>13.10380030241145</v>
+        <v>12.96496341211036</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.667503376833933</v>
+        <v>1.530536884129684</v>
       </c>
       <c r="C5" t="n">
-        <v>5.894236459490752</v>
+        <v>6.102358192438037</v>
       </c>
       <c r="D5" t="n">
-        <v>6.773263942069332</v>
+        <v>6.589780892344834</v>
       </c>
       <c r="E5" t="n">
-        <v>14.33500377839402</v>
+        <v>14.22267596891255</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.910459401532144</v>
+        <v>1.709497086535709</v>
       </c>
       <c r="C6" t="n">
-        <v>6.717000569986133</v>
+        <v>7.077227313273459</v>
       </c>
       <c r="D6" t="n">
-        <v>7.155489732731707</v>
+        <v>6.919284049474906</v>
       </c>
       <c r="E6" t="n">
-        <v>15.78294970424998</v>
+        <v>15.70600844928407</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.185475746086786</v>
+        <v>1.90278228783935</v>
       </c>
       <c r="C7" t="n">
-        <v>7.70366821488343</v>
+        <v>8.185708239799567</v>
       </c>
       <c r="D7" t="n">
-        <v>7.53915717406427</v>
+        <v>7.238824453270243</v>
       </c>
       <c r="E7" t="n">
-        <v>17.42830113503449</v>
+        <v>17.32731498090916</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.373448331546851</v>
+        <v>1.114811889616341</v>
       </c>
       <c r="C8" t="n">
-        <v>5.316849041892524</v>
+        <v>5.744889969055859</v>
       </c>
       <c r="D8" t="n">
-        <v>5.705202811420642</v>
+        <v>5.49055538540031</v>
       </c>
       <c r="E8" t="n">
-        <v>12.39550018486002</v>
+        <v>12.35025724407251</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.739241946420819</v>
+        <v>1.373698037858811</v>
       </c>
       <c r="C9" t="n">
-        <v>6.535266927088039</v>
+        <v>7.075213766444687</v>
       </c>
       <c r="D9" t="n">
-        <v>6.232782845811256</v>
+        <v>5.948331289710723</v>
       </c>
       <c r="E9" t="n">
-        <v>14.50729171932011</v>
+        <v>14.39724309401422</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.120636156313392</v>
+        <v>1.65024193076187</v>
       </c>
       <c r="C10" t="n">
-        <v>7.904397154892007</v>
+        <v>8.578353929712192</v>
       </c>
       <c r="D10" t="n">
-        <v>6.716865699231477</v>
+        <v>6.470264498234244</v>
       </c>
       <c r="E10" t="n">
-        <v>16.74189901043687</v>
+        <v>16.69886035870831</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.519330313545692</v>
+        <v>1.93877852813675</v>
       </c>
       <c r="C11" t="n">
-        <v>9.371652176135441</v>
+        <v>10.1784667119295</v>
       </c>
       <c r="D11" t="n">
-        <v>7.145246956140323</v>
+        <v>7.003457854713366</v>
       </c>
       <c r="E11" t="n">
-        <v>19.03622944582145</v>
+        <v>19.12070309477961</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.911955560704671</v>
+        <v>2.21920398542309</v>
       </c>
       <c r="C12" t="n">
-        <v>10.96122520885195</v>
+        <v>11.84431844763091</v>
       </c>
       <c r="D12" t="n">
-        <v>7.724270943058397</v>
+        <v>7.455954553358212</v>
       </c>
       <c r="E12" t="n">
-        <v>21.59745171261502</v>
+        <v>21.51947698641221</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.275648394657826</v>
+        <v>2.482519479292711</v>
       </c>
       <c r="C13" t="n">
-        <v>12.55093632685828</v>
+        <v>13.58737962721377</v>
       </c>
       <c r="D13" t="n">
-        <v>8.253297764635503</v>
+        <v>7.870297762074205</v>
       </c>
       <c r="E13" t="n">
-        <v>24.07988248615161</v>
+        <v>23.94019686858068</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.878377882535422</v>
+        <v>1.433763982236127</v>
       </c>
       <c r="C14" t="n">
-        <v>8.821493996509714</v>
+        <v>9.56944830246719</v>
       </c>
       <c r="D14" t="n">
-        <v>6.246575935288223</v>
+        <v>5.999381680835919</v>
       </c>
       <c r="E14" t="n">
-        <v>16.94644781433336</v>
+        <v>17.00259396553924</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.925334875229547</v>
+        <v>1.447979688993621</v>
       </c>
       <c r="C15" t="n">
-        <v>9.526182681141032</v>
+        <v>10.34225064281915</v>
       </c>
       <c r="D15" t="n">
-        <v>6.279925904801487</v>
+        <v>5.981818214406943</v>
       </c>
       <c r="E15" t="n">
-        <v>17.73144346117207</v>
+        <v>17.77204854621971</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.247642646533775</v>
+        <v>1.659889930955295</v>
       </c>
       <c r="C16" t="n">
-        <v>11.22976038493531</v>
+        <v>12.18129971232245</v>
       </c>
       <c r="D16" t="n">
-        <v>6.800487807501317</v>
+        <v>6.38443294791856</v>
       </c>
       <c r="E16" t="n">
-        <v>20.2778908389704</v>
+        <v>20.2256225911963</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.813081842725967</v>
+        <v>1.316896735522586</v>
       </c>
       <c r="C17" t="n">
-        <v>10.3110997881634</v>
+        <v>11.14811824585015</v>
       </c>
       <c r="D17" t="n">
-        <v>6.334010385828444</v>
+        <v>5.890878924562561</v>
       </c>
       <c r="E17" t="n">
-        <v>18.45819201671781</v>
+        <v>18.35589390593529</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.083327533273986</v>
+        <v>1.488800758536203</v>
       </c>
       <c r="C18" t="n">
-        <v>11.99350119397707</v>
+        <v>12.99308725401005</v>
       </c>
       <c r="D18" t="n">
-        <v>6.825443834143269</v>
+        <v>6.251838102982986</v>
       </c>
       <c r="E18" t="n">
-        <v>20.90227256139433</v>
+        <v>20.73372611552924</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.102854495111456</v>
+        <v>1.481447468231395</v>
       </c>
       <c r="C19" t="n">
-        <v>12.77503127141979</v>
+        <v>13.87086787637712</v>
       </c>
       <c r="D19" t="n">
-        <v>6.946915477589727</v>
+        <v>6.313521311240813</v>
       </c>
       <c r="E19" t="n">
-        <v>21.82480124412097</v>
+        <v>21.66583665584933</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.349116089244725</v>
+        <v>1.641629423656304</v>
       </c>
       <c r="C20" t="n">
-        <v>14.60593183497784</v>
+        <v>15.89079414291085</v>
       </c>
       <c r="D20" t="n">
-        <v>7.380671248280053</v>
+        <v>6.659086685658647</v>
       </c>
       <c r="E20" t="n">
-        <v>24.33571917250261</v>
+        <v>24.1915102522258</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.403869764641811</v>
+        <v>0.9738740876587512</v>
       </c>
       <c r="C21" t="n">
-        <v>10.68576416453511</v>
+        <v>11.66038438044909</v>
       </c>
       <c r="D21" t="n">
-        <v>6.182065293642165</v>
+        <v>5.529438689767055</v>
       </c>
       <c r="E21" t="n">
-        <v>18.27169922281909</v>
+        <v>18.16369715787489</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_18_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_18_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.252078252369293</v>
+        <v>1.289090140819398</v>
       </c>
       <c r="C3" t="n">
-        <v>4.681068174436266</v>
+        <v>4.639324262051691</v>
       </c>
       <c r="D3" t="n">
-        <v>6.09171023761645</v>
+        <v>6.145961615753129</v>
       </c>
       <c r="E3" t="n">
-        <v>12.02485666442201</v>
+        <v>12.07437601862422</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.370120514045453</v>
+        <v>1.463005006257148</v>
       </c>
       <c r="C4" t="n">
-        <v>5.300078362317505</v>
+        <v>5.136582814966374</v>
       </c>
       <c r="D4" t="n">
-        <v>6.294764535747397</v>
+        <v>6.380254128708016</v>
       </c>
       <c r="E4" t="n">
-        <v>12.96496341211036</v>
+        <v>12.97984194993154</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.530536884129684</v>
+        <v>1.688546463441679</v>
       </c>
       <c r="C5" t="n">
-        <v>6.102358192438037</v>
+        <v>5.803336288315811</v>
       </c>
       <c r="D5" t="n">
-        <v>6.589780892344834</v>
+        <v>6.675700813280816</v>
       </c>
       <c r="E5" t="n">
-        <v>14.22267596891255</v>
+        <v>14.16758356503831</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.709497086535709</v>
+        <v>1.939724019742477</v>
       </c>
       <c r="C6" t="n">
-        <v>7.077227313273459</v>
+        <v>6.618440013490403</v>
       </c>
       <c r="D6" t="n">
-        <v>6.919284049474906</v>
+        <v>7.085453985666684</v>
       </c>
       <c r="E6" t="n">
-        <v>15.70600844928407</v>
+        <v>15.64361801889956</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.90278228783935</v>
+        <v>2.215802470876765</v>
       </c>
       <c r="C7" t="n">
-        <v>8.185708239799567</v>
+        <v>7.607776480280317</v>
       </c>
       <c r="D7" t="n">
-        <v>7.238824453270243</v>
+        <v>7.44323733026894</v>
       </c>
       <c r="E7" t="n">
-        <v>17.32731498090916</v>
+        <v>17.26681628142602</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.114811889616341</v>
+        <v>1.380481012444589</v>
       </c>
       <c r="C8" t="n">
-        <v>5.744889969055859</v>
+        <v>5.327278105798594</v>
       </c>
       <c r="D8" t="n">
-        <v>5.49055538540031</v>
+        <v>5.710452357484422</v>
       </c>
       <c r="E8" t="n">
-        <v>12.35025724407251</v>
+        <v>12.4182114757276</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.373698037858811</v>
+        <v>1.72145498993255</v>
       </c>
       <c r="C9" t="n">
-        <v>7.075213766444687</v>
+        <v>6.643625502716625</v>
       </c>
       <c r="D9" t="n">
-        <v>5.948331289710723</v>
+        <v>6.21098978071149</v>
       </c>
       <c r="E9" t="n">
-        <v>14.39724309401422</v>
+        <v>14.57607027336066</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.65024193076187</v>
+        <v>2.067216589229145</v>
       </c>
       <c r="C10" t="n">
-        <v>8.578353929712192</v>
+        <v>8.187408553470991</v>
       </c>
       <c r="D10" t="n">
-        <v>6.470264498234244</v>
+        <v>6.711959529264607</v>
       </c>
       <c r="E10" t="n">
-        <v>16.69886035870831</v>
+        <v>16.96658467196474</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.93877852813675</v>
+        <v>2.417385194260075</v>
       </c>
       <c r="C11" t="n">
-        <v>10.1784667119295</v>
+        <v>9.896985997979694</v>
       </c>
       <c r="D11" t="n">
-        <v>7.003457854713366</v>
+        <v>7.164616400668484</v>
       </c>
       <c r="E11" t="n">
-        <v>19.12070309477961</v>
+        <v>19.47898759290825</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.21920398542309</v>
+        <v>2.755391703811816</v>
       </c>
       <c r="C12" t="n">
-        <v>11.84431844763091</v>
+        <v>11.69848233387018</v>
       </c>
       <c r="D12" t="n">
-        <v>7.455954553358212</v>
+        <v>7.642642092433995</v>
       </c>
       <c r="E12" t="n">
-        <v>21.51947698641221</v>
+        <v>22.09651613011599</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.482519479292711</v>
+        <v>3.068370145336129</v>
       </c>
       <c r="C13" t="n">
-        <v>13.58737962721377</v>
+        <v>13.50827679323634</v>
       </c>
       <c r="D13" t="n">
-        <v>7.870297762074205</v>
+        <v>8.063422983609826</v>
       </c>
       <c r="E13" t="n">
-        <v>23.94019686858068</v>
+        <v>24.64006992218229</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.433763982236127</v>
+        <v>1.777630933125615</v>
       </c>
       <c r="C14" t="n">
-        <v>9.56944830246719</v>
+        <v>9.378194032202869</v>
       </c>
       <c r="D14" t="n">
-        <v>5.999381680835919</v>
+        <v>6.109003629492117</v>
       </c>
       <c r="E14" t="n">
-        <v>17.00259396553924</v>
+        <v>17.2648285948206</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.447979688993621</v>
+        <v>1.795665638452629</v>
       </c>
       <c r="C15" t="n">
-        <v>10.34225064281915</v>
+        <v>10.29093469031817</v>
       </c>
       <c r="D15" t="n">
-        <v>5.981818214406943</v>
+        <v>6.08363526881438</v>
       </c>
       <c r="E15" t="n">
-        <v>17.77204854621971</v>
+        <v>18.17023559758518</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.659889930955295</v>
+        <v>2.053992911871092</v>
       </c>
       <c r="C16" t="n">
-        <v>12.18129971232245</v>
+        <v>12.21783054439747</v>
       </c>
       <c r="D16" t="n">
-        <v>6.38443294791856</v>
+        <v>6.498492396197956</v>
       </c>
       <c r="E16" t="n">
-        <v>20.2256225911963</v>
+        <v>20.77031585246652</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.316896735522586</v>
+        <v>1.623447456173653</v>
       </c>
       <c r="C17" t="n">
-        <v>11.14811824585015</v>
+        <v>11.31388634571222</v>
       </c>
       <c r="D17" t="n">
-        <v>5.890878924562561</v>
+        <v>6.004545673760257</v>
       </c>
       <c r="E17" t="n">
-        <v>18.35589390593529</v>
+        <v>18.94187947564613</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.488800758536203</v>
+        <v>1.838077139276091</v>
       </c>
       <c r="C18" t="n">
-        <v>12.99308725401005</v>
+        <v>13.19101740866325</v>
       </c>
       <c r="D18" t="n">
-        <v>6.251838102982986</v>
+        <v>6.390068179740936</v>
       </c>
       <c r="E18" t="n">
-        <v>20.73372611552924</v>
+        <v>21.41916272768028</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.481447468231395</v>
+        <v>1.82844619429743</v>
       </c>
       <c r="C19" t="n">
-        <v>13.87086787637712</v>
+        <v>14.09608079973134</v>
       </c>
       <c r="D19" t="n">
-        <v>6.313521311240813</v>
+        <v>6.445163860903269</v>
       </c>
       <c r="E19" t="n">
-        <v>21.66583665584933</v>
+        <v>22.36969085493204</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.641629423656304</v>
+        <v>2.022468993087727</v>
       </c>
       <c r="C20" t="n">
-        <v>15.89079414291085</v>
+        <v>16.08046779937133</v>
       </c>
       <c r="D20" t="n">
-        <v>6.659086685658647</v>
+        <v>6.845530392172159</v>
       </c>
       <c r="E20" t="n">
-        <v>24.1915102522258</v>
+        <v>24.94846718463122</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9738740876587512</v>
+        <v>1.199509162525796</v>
       </c>
       <c r="C21" t="n">
-        <v>11.66038438044909</v>
+        <v>11.66808128245038</v>
       </c>
       <c r="D21" t="n">
-        <v>5.529438689767055</v>
+        <v>5.687264450701773</v>
       </c>
       <c r="E21" t="n">
-        <v>18.16369715787489</v>
+        <v>18.55485489567795</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_18_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_18_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.289090140819398</v>
+        <v>2.596614207368876</v>
       </c>
       <c r="C3" t="n">
-        <v>4.639324262051691</v>
+        <v>7.684342617514182</v>
       </c>
       <c r="D3" t="n">
-        <v>6.145961615753129</v>
+        <v>8.276837810205091</v>
       </c>
       <c r="E3" t="n">
-        <v>12.07437601862422</v>
+        <v>18.55779463508815</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.463005006257148</v>
+        <v>1.085531675481873</v>
       </c>
       <c r="C4" t="n">
-        <v>5.136582814966374</v>
+        <v>4.426245413838771</v>
       </c>
       <c r="D4" t="n">
-        <v>6.380254128708016</v>
+        <v>6.015953155679743</v>
       </c>
       <c r="E4" t="n">
-        <v>12.97984194993154</v>
+        <v>11.52773024500039</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.688546463441679</v>
+        <v>1.190817799518096</v>
       </c>
       <c r="C5" t="n">
-        <v>5.803336288315811</v>
+        <v>4.951673156773398</v>
       </c>
       <c r="D5" t="n">
-        <v>6.675700813280816</v>
+        <v>6.48772055070111</v>
       </c>
       <c r="E5" t="n">
-        <v>14.16758356503831</v>
+        <v>12.6302115069926</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.939724019742477</v>
+        <v>1.301904132659591</v>
       </c>
       <c r="C6" t="n">
-        <v>6.618440013490403</v>
+        <v>5.60808202448942</v>
       </c>
       <c r="D6" t="n">
-        <v>7.085453985666684</v>
+        <v>6.963909311113714</v>
       </c>
       <c r="E6" t="n">
-        <v>15.64361801889956</v>
+        <v>13.87389546826273</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.215802470876765</v>
+        <v>1.417812297855058</v>
       </c>
       <c r="C7" t="n">
-        <v>7.607776480280317</v>
+        <v>6.366649349137742</v>
       </c>
       <c r="D7" t="n">
-        <v>7.44323733026894</v>
+        <v>7.466106394983296</v>
       </c>
       <c r="E7" t="n">
-        <v>17.26681628142602</v>
+        <v>15.25056804197609</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.380481012444589</v>
+        <v>1.555281612923678</v>
       </c>
       <c r="C8" t="n">
-        <v>5.327278105798594</v>
+        <v>7.253981771536125</v>
       </c>
       <c r="D8" t="n">
-        <v>5.710452357484422</v>
+        <v>8.009943753604361</v>
       </c>
       <c r="E8" t="n">
-        <v>12.4182114757276</v>
+        <v>16.81920713806417</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.72145498993255</v>
+        <v>1.686259316998591</v>
       </c>
       <c r="C9" t="n">
-        <v>6.643625502716625</v>
+        <v>8.254822564120708</v>
       </c>
       <c r="D9" t="n">
-        <v>6.21098978071149</v>
+        <v>8.576978408709634</v>
       </c>
       <c r="E9" t="n">
-        <v>14.57607027336066</v>
+        <v>18.51806028982893</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.067216589229145</v>
+        <v>1.060915839117273</v>
       </c>
       <c r="C10" t="n">
-        <v>8.187408553470991</v>
+        <v>6.210545794542364</v>
       </c>
       <c r="D10" t="n">
-        <v>6.711959529264607</v>
+        <v>6.764732556112646</v>
       </c>
       <c r="E10" t="n">
-        <v>16.96658467196474</v>
+        <v>14.03619418977228</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.417385194260075</v>
+        <v>0.9931359776160734</v>
       </c>
       <c r="C11" t="n">
-        <v>9.896985997979694</v>
+        <v>6.438821770733833</v>
       </c>
       <c r="D11" t="n">
-        <v>7.164616400668484</v>
+        <v>6.73800938360305</v>
       </c>
       <c r="E11" t="n">
-        <v>19.47898759290825</v>
+        <v>14.16996713195296</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.755391703811816</v>
+        <v>1.068436026531804</v>
       </c>
       <c r="C12" t="n">
-        <v>11.69848233387018</v>
+        <v>7.481850166679729</v>
       </c>
       <c r="D12" t="n">
-        <v>7.642642092433995</v>
+        <v>7.263185500512838</v>
       </c>
       <c r="E12" t="n">
-        <v>22.09651613011599</v>
+        <v>15.81347169372437</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.068370145336129</v>
+        <v>0.8395415492866599</v>
       </c>
       <c r="C13" t="n">
-        <v>13.50827679323634</v>
+        <v>7.04190938545265</v>
       </c>
       <c r="D13" t="n">
-        <v>8.063422983609826</v>
+        <v>6.757497075532347</v>
       </c>
       <c r="E13" t="n">
-        <v>24.64006992218229</v>
+        <v>14.63894801027166</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.777630933125615</v>
+        <v>0.9116607356406307</v>
       </c>
       <c r="C14" t="n">
-        <v>9.378194032202869</v>
+        <v>8.146915513967647</v>
       </c>
       <c r="D14" t="n">
-        <v>6.109003629492117</v>
+        <v>7.263882541382853</v>
       </c>
       <c r="E14" t="n">
-        <v>17.2648285948206</v>
+        <v>16.32245879099113</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.795665638452629</v>
+        <v>0.8848688407917352</v>
       </c>
       <c r="C15" t="n">
-        <v>10.29093469031817</v>
+        <v>8.707915604605402</v>
       </c>
       <c r="D15" t="n">
-        <v>6.08363526881438</v>
+        <v>7.420903269200086</v>
       </c>
       <c r="E15" t="n">
-        <v>18.17023559758518</v>
+        <v>17.01368771459722</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.053992911871092</v>
+        <v>0.9782526824196919</v>
       </c>
       <c r="C16" t="n">
-        <v>12.21783054439747</v>
+        <v>10.19196470425305</v>
       </c>
       <c r="D16" t="n">
-        <v>6.498492396197956</v>
+        <v>7.948847914635851</v>
       </c>
       <c r="E16" t="n">
-        <v>20.77031585246652</v>
+        <v>19.11906530130859</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.623447456173653</v>
+        <v>0.5961073885416208</v>
       </c>
       <c r="C17" t="n">
-        <v>11.31388634571222</v>
+        <v>7.750593783240252</v>
       </c>
       <c r="D17" t="n">
-        <v>6.004545673760257</v>
+        <v>6.674519759569408</v>
       </c>
       <c r="E17" t="n">
-        <v>18.94187947564613</v>
+        <v>15.02122093135128</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.838077139276091</v>
+        <v>0.4727606069800515</v>
       </c>
       <c r="C18" t="n">
-        <v>13.19101740866325</v>
+        <v>6.883023336997346</v>
       </c>
       <c r="D18" t="n">
-        <v>6.390068179740936</v>
+        <v>6.160790820891137</v>
       </c>
       <c r="E18" t="n">
-        <v>21.41916272768028</v>
+        <v>13.51657476486854</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.82844619429743</v>
+        <v>0.5556790180807372</v>
       </c>
       <c r="C19" t="n">
-        <v>14.09608079973134</v>
+        <v>8.568615422849822</v>
       </c>
       <c r="D19" t="n">
-        <v>6.445163860903269</v>
+        <v>6.848819246981386</v>
       </c>
       <c r="E19" t="n">
-        <v>22.36969085493204</v>
+        <v>15.97311368791195</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.022468993087727</v>
+        <v>0.6331978168080653</v>
       </c>
       <c r="C20" t="n">
-        <v>16.08046779937133</v>
+        <v>10.35394325797673</v>
       </c>
       <c r="D20" t="n">
-        <v>6.845530392172159</v>
+        <v>7.491392754365009</v>
       </c>
       <c r="E20" t="n">
-        <v>24.94846718463122</v>
+        <v>18.4785338291498</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.199509162525796</v>
+        <v>0.699505056752895</v>
       </c>
       <c r="C21" t="n">
-        <v>11.66808128245038</v>
+        <v>12.16028049397452</v>
       </c>
       <c r="D21" t="n">
-        <v>5.687264450701773</v>
+        <v>8.121704232922589</v>
       </c>
       <c r="E21" t="n">
-        <v>18.55485489567795</v>
+        <v>20.98148978365001</v>
       </c>
     </row>
   </sheetData>
